--- a/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0033.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/quest/lang_multi_text/lang_multi_text__quest__part_0033.xlsx
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
